--- a/artfynd/A 40934-2025 artfynd.xlsx
+++ b/artfynd/A 40934-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128622556</v>
       </c>
       <c r="B2" t="n">
-        <v>79115</v>
+        <v>79119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128622558</v>
       </c>
       <c r="B3" t="n">
-        <v>91417</v>
+        <v>91423</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128622559</v>
       </c>
       <c r="B4" t="n">
-        <v>90485</v>
+        <v>90491</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128622570</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128622561</v>
       </c>
       <c r="B6" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128622560</v>
       </c>
       <c r="B7" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128622571</v>
       </c>
       <c r="B8" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128622564</v>
       </c>
       <c r="B9" t="n">
-        <v>91402</v>
+        <v>91408</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128622568</v>
       </c>
       <c r="B10" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128622565</v>
       </c>
       <c r="B11" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40934-2025 artfynd.xlsx
+++ b/artfynd/A 40934-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128622558</v>
       </c>
       <c r="B3" t="n">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128622559</v>
       </c>
       <c r="B4" t="n">
-        <v>90491</v>
+        <v>90497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128622561</v>
       </c>
       <c r="B6" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128622560</v>
       </c>
       <c r="B7" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128622564</v>
       </c>
       <c r="B9" t="n">
-        <v>91408</v>
+        <v>91414</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 40934-2025 artfynd.xlsx
+++ b/artfynd/A 40934-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128622556</v>
       </c>
       <c r="B2" t="n">
-        <v>79119</v>
+        <v>79121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128622558</v>
       </c>
       <c r="B3" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128622559</v>
       </c>
       <c r="B4" t="n">
-        <v>90497</v>
+        <v>90499</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128622570</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128622561</v>
       </c>
       <c r="B6" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128622560</v>
       </c>
       <c r="B7" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128622571</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128622564</v>
       </c>
       <c r="B9" t="n">
-        <v>91414</v>
+        <v>91416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128622568</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 40934-2025 artfynd.xlsx
+++ b/artfynd/A 40934-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128622558</v>
       </c>
       <c r="B3" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128622561</v>
       </c>
       <c r="B6" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128622560</v>
       </c>
       <c r="B7" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128622564</v>
       </c>
       <c r="B9" t="n">
-        <v>91416</v>
+        <v>91417</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 40934-2025 artfynd.xlsx
+++ b/artfynd/A 40934-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128622556</v>
       </c>
       <c r="B2" t="n">
-        <v>79121</v>
+        <v>79148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128622558</v>
       </c>
       <c r="B3" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128622559</v>
       </c>
       <c r="B4" t="n">
-        <v>90499</v>
+        <v>90526</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128622570</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128622561</v>
       </c>
       <c r="B6" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128622560</v>
       </c>
       <c r="B7" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128622571</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128622564</v>
       </c>
       <c r="B9" t="n">
-        <v>91417</v>
+        <v>91444</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128622568</v>
       </c>
       <c r="B10" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128622565</v>
       </c>
       <c r="B11" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40934-2025 artfynd.xlsx
+++ b/artfynd/A 40934-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128622556</v>
       </c>
       <c r="B2" t="n">
-        <v>79148</v>
+        <v>79152</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128622558</v>
       </c>
       <c r="B3" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128622559</v>
       </c>
       <c r="B4" t="n">
-        <v>90526</v>
+        <v>90531</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128622570</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128622561</v>
       </c>
       <c r="B6" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128622560</v>
       </c>
       <c r="B7" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128622571</v>
       </c>
       <c r="B8" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128622564</v>
       </c>
       <c r="B9" t="n">
-        <v>91444</v>
+        <v>91449</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128622568</v>
       </c>
       <c r="B10" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 40934-2025 artfynd.xlsx
+++ b/artfynd/A 40934-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128622558</v>
       </c>
       <c r="B3" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128622559</v>
       </c>
       <c r="B4" t="n">
-        <v>90531</v>
+        <v>90536</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128622561</v>
       </c>
       <c r="B6" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128622560</v>
       </c>
       <c r="B7" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128622564</v>
       </c>
       <c r="B9" t="n">
-        <v>91449</v>
+        <v>91454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 40934-2025 artfynd.xlsx
+++ b/artfynd/A 40934-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128622556</v>
       </c>
       <c r="B2" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128622558</v>
       </c>
       <c r="B3" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128622559</v>
       </c>
       <c r="B4" t="n">
-        <v>90536</v>
+        <v>90540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128622570</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128622561</v>
       </c>
       <c r="B6" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128622560</v>
       </c>
       <c r="B7" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128622571</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128622564</v>
       </c>
       <c r="B9" t="n">
-        <v>91454</v>
+        <v>91458</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128622568</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128622565</v>
       </c>
       <c r="B11" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40934-2025 artfynd.xlsx
+++ b/artfynd/A 40934-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128622556</v>
       </c>
       <c r="B2" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128622558</v>
       </c>
       <c r="B3" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128622559</v>
       </c>
       <c r="B4" t="n">
-        <v>90540</v>
+        <v>90545</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128622570</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128622561</v>
       </c>
       <c r="B6" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128622560</v>
       </c>
       <c r="B7" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128622571</v>
       </c>
       <c r="B8" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128622564</v>
       </c>
       <c r="B9" t="n">
-        <v>91458</v>
+        <v>91463</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128622568</v>
       </c>
       <c r="B10" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128622565</v>
       </c>
       <c r="B11" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40934-2025 artfynd.xlsx
+++ b/artfynd/A 40934-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128622556</v>
       </c>
       <c r="B2" t="n">
-        <v>79061</v>
+        <v>79066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128622558</v>
       </c>
       <c r="B3" t="n">
-        <v>91480</v>
+        <v>91485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128622559</v>
       </c>
       <c r="B4" t="n">
-        <v>90547</v>
+        <v>90552</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128622570</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128622561</v>
       </c>
       <c r="B6" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128622560</v>
       </c>
       <c r="B7" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128622571</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128622564</v>
       </c>
       <c r="B9" t="n">
-        <v>91465</v>
+        <v>91470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128622568</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 40934-2025 artfynd.xlsx
+++ b/artfynd/A 40934-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128622556</v>
       </c>
       <c r="B2" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128622558</v>
       </c>
       <c r="B3" t="n">
-        <v>91485</v>
+        <v>91491</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128622559</v>
       </c>
       <c r="B4" t="n">
-        <v>90552</v>
+        <v>90558</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128622570</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128622561</v>
       </c>
       <c r="B6" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128622560</v>
       </c>
       <c r="B7" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128622571</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128622564</v>
       </c>
       <c r="B9" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128622568</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
